--- a/New Google Scholar List.xlsx
+++ b/New Google Scholar List.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="60" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$I$109</definedName>
@@ -609,17 +609,17 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1387</v>
+        <v>1455</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>2026-08-04 23:15:29</t>
+          <t>2026-09-14 19:02:16</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>695</v>
+        <v>737</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>16</v>
@@ -665,7 +665,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-08-04 23:15:43</t>
+          <t>2026-09-14 19:02:29</t>
         </is>
       </c>
     </row>
@@ -701,17 +701,17 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>6127</v>
+        <v>6333</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-04 23:15:51</t>
+          <t>2026-09-14 19:02:38</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>2106</v>
+        <v>2148</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>21</v>
@@ -757,7 +757,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:03</t>
+          <t>2026-09-14 19:02:48</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1453</v>
+        <v>1494</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>20</v>
@@ -803,7 +803,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:12</t>
+          <t>2026-09-14 19:03:00</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>540</v>
+        <v>563</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>15</v>
@@ -849,7 +849,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:22</t>
+          <t>2026-09-14 19:03:12</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1399</v>
+        <v>1468</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>14</v>
@@ -895,7 +895,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:30</t>
+          <t>2026-09-14 19:03:24</t>
         </is>
       </c>
     </row>
@@ -931,17 +931,17 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:38</t>
+          <t>2026-09-14 19:03:31</t>
         </is>
       </c>
     </row>
@@ -977,17 +977,17 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>844</v>
+        <v>871</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-04 23:16:49</t>
+          <t>2026-09-14 19:03:46</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>695</v>
+        <v>712</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>14</v>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-04 23:17:02</t>
+          <t>2026-09-14 19:04:00</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>353</v>
+        <v>380</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>6</v>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-04 23:17:11</t>
+          <t>2026-09-14 19:04:12</t>
         </is>
       </c>
     </row>
@@ -1115,17 +1115,17 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1896</v>
+        <v>1931</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>38</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-04 23:17:25</t>
+          <t>2026-09-14 19:04:22</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>4</v>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-04 23:17:39</t>
+          <t>2026-09-14 19:04:35</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>380</v>
+        <v>395</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I15" s="2" t="n">
         <v>7</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-04 23:17:47</t>
+          <t>2026-09-14 19:04:44</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>767</v>
+        <v>795</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>15</v>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-04 23:17:57</t>
+          <t>2026-09-14 19:04:55</t>
         </is>
       </c>
     </row>
@@ -1299,17 +1299,17 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>6</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-04 23:18:07</t>
+          <t>2026-09-14 19:05:10</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>5</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-04 23:18:19</t>
+          <t>2026-09-14 19:05:18</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>7</v>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-04 23:18:30</t>
+          <t>2026-09-14 19:05:24</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>4</v>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-08-04 23:18:44</t>
+          <t>2026-09-14 19:05:32</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1746</v>
+        <v>1871</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-04 23:18:56</t>
+          <t>2026-09-14 19:05:40</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1480</v>
+        <v>1515</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>23</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-04 23:19:10</t>
+          <t>2026-09-14 19:05:45</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>1418</v>
+        <v>1446</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>20</v>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-04 23:19:21</t>
+          <t>2026-09-14 19:05:57</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>1418</v>
+        <v>1446</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>20</v>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-04 23:19:26</t>
+          <t>2026-09-14 19:06:06</t>
         </is>
       </c>
     </row>
@@ -1667,17 +1667,17 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>676</v>
+        <v>707</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>14</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-04 23:19:34</t>
+          <t>2026-09-14 19:06:13</t>
         </is>
       </c>
     </row>
@@ -1713,17 +1713,17 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>1852</v>
+        <v>1894</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I26" s="2" t="n">
         <v>36</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-04 23:19:48</t>
+          <t>2026-09-14 19:06:24</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>12</v>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-04 23:20:02</t>
+          <t>2026-09-14 19:06:35</t>
         </is>
       </c>
     </row>
@@ -1805,17 +1805,17 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>1878</v>
+        <v>1947</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-04 23:20:12</t>
+          <t>2026-09-14 19:06:41</t>
         </is>
       </c>
     </row>
@@ -1851,17 +1851,17 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>1301</v>
+        <v>1334</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-04 23:20:20</t>
+          <t>2026-09-14 19:06:48</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>606</v>
+        <v>635</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>11</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-04 23:20:28</t>
+          <t>2026-09-14 19:06:59</t>
         </is>
       </c>
     </row>
@@ -1943,17 +1943,17 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>2962</v>
+        <v>3057</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-04 23:20:33</t>
+          <t>2026-09-14 19:07:05</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-04 23:20:47</t>
+          <t>2026-09-14 19:07:14</t>
         </is>
       </c>
     </row>
@@ -2035,17 +2035,17 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>7</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-04 23:21:00</t>
+          <t>2026-09-14 19:07:28</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>1001</v>
+        <v>1033</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>15</v>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-04 23:21:13</t>
+          <t>2026-09-14 19:07:34</t>
         </is>
       </c>
     </row>
@@ -2127,17 +2127,17 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>1541</v>
+        <v>1573</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>21</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-04 23:21:21</t>
+          <t>2026-09-14 19:07:42</t>
         </is>
       </c>
     </row>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>10</v>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-04 23:21:34</t>
+          <t>2026-09-14 19:07:50</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>1457</v>
+        <v>1495</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>17</v>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-04 23:21:47</t>
+          <t>2026-09-14 19:07:59</t>
         </is>
       </c>
     </row>
@@ -2265,17 +2265,17 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>1580</v>
+        <v>1642</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>18</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-04 23:22:01</t>
+          <t>2026-09-14 19:08:07</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>12</v>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-04 23:22:16</t>
+          <t>2026-09-14 19:08:21</t>
         </is>
       </c>
     </row>
@@ -2357,17 +2357,17 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>3758</v>
+        <v>3854</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-04 23:22:25</t>
+          <t>2026-09-14 19:08:28</t>
         </is>
       </c>
     </row>
@@ -2403,17 +2403,17 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>3116</v>
+        <v>3274</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>28</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-04 23:22:38</t>
+          <t>2026-09-14 19:08:42</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>693</v>
+        <v>720</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>13</v>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-04 23:22:45</t>
+          <t>2026-09-14 19:08:53</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>9</v>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-04 23:22:53</t>
+          <t>2026-09-14 19:09:07</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>445</v>
+        <v>461</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>10</v>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:07</t>
+          <t>2026-09-14 19:09:17</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:18</t>
+          <t>2026-09-14 19:09:25</t>
         </is>
       </c>
     </row>
@@ -2668,17 +2668,17 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>2268</v>
+        <v>2355</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:25</t>
+          <t>2026-09-14 19:09:31</t>
         </is>
       </c>
     </row>
@@ -2714,17 +2714,17 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>2259</v>
+        <v>2319</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>28</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:38</t>
+          <t>2026-09-14 19:09:44</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>1205</v>
+        <v>1254</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>17</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:52</t>
+          <t>2026-09-14 19:09:52</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>7</v>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-08-04 23:23:57</t>
+          <t>2026-09-14 19:09:58</t>
         </is>
       </c>
     </row>
@@ -2852,17 +2852,17 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I51" s="2" t="n">
         <v>3</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-08-04 23:24:04</t>
+          <t>2026-09-14 19:10:04</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>1046</v>
+        <v>1114</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>13</v>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-08-04 23:24:17</t>
+          <t>2026-09-14 19:10:13</t>
         </is>
       </c>
     </row>
@@ -2944,17 +2944,17 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>2837</v>
+        <v>2940</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-08-04 23:24:26</t>
+          <t>2026-09-14 19:10:19</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>4394</v>
+        <v>4500</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>37</v>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-08-04 23:24:33</t>
+          <t>2026-09-14 19:10:29</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>6</v>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-08-04 23:24:45</t>
+          <t>2026-09-14 19:10:35</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>7</v>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-08-04 23:24:55</t>
+          <t>2026-09-14 19:10:45</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>2</v>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-08-04 23:25:01</t>
+          <t>2026-09-14 19:10:53</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>1933</v>
+        <v>1985</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>22</v>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-08-04 23:25:09</t>
+          <t>2026-09-14 19:11:08</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>509</v>
+        <v>525</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>12</v>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-08-04 23:25:20</t>
+          <t>2026-09-14 19:11:16</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>1023</v>
+        <v>1077</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>17</v>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-08-04 23:25:30</t>
+          <t>2026-09-14 19:11:23</t>
         </is>
       </c>
     </row>
@@ -3312,17 +3312,17 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>2226</v>
+        <v>2301</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-08-04 23:25:40</t>
+          <t>2026-09-14 19:11:29</t>
         </is>
       </c>
     </row>
@@ -3358,17 +3358,17 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>1547</v>
+        <v>1580</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>22</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-08-04 23:25:46</t>
+          <t>2026-09-14 19:11:42</t>
         </is>
       </c>
     </row>
@@ -3404,17 +3404,17 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>1170</v>
+        <v>1214</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-08-04 23:25:58</t>
+          <t>2026-09-14 19:11:50</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>9</v>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-08-04 23:26:08</t>
+          <t>2026-09-14 19:12:05</t>
         </is>
       </c>
     </row>
@@ -3496,17 +3496,17 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>7256</v>
+        <v>7441</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-08-04 23:26:20</t>
+          <t>2026-09-14 19:12:19</t>
         </is>
       </c>
     </row>
@@ -3542,17 +3542,17 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>1262</v>
+        <v>1310</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>19</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-08-04 23:26:26</t>
+          <t>2026-09-14 19:12:31</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>2190</v>
+        <v>2244</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>28</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-08-04 23:26:41</t>
+          <t>2026-09-14 19:12:42</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3634,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>8</v>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-08-04 23:26:54</t>
+          <t>2026-09-14 19:12:55</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>536</v>
+        <v>555</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>11</v>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-08-04 23:27:06</t>
+          <t>2026-09-14 19:13:08</t>
         </is>
       </c>
     </row>
@@ -3726,17 +3726,17 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>502</v>
+        <v>520</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>11</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-08-04 23:27:17</t>
+          <t>2026-09-14 19:13:18</t>
         </is>
       </c>
     </row>
@@ -3772,17 +3772,17 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>4058</v>
+        <v>4208</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-08-04 23:27:26</t>
+          <t>2026-09-14 19:13:24</t>
         </is>
       </c>
     </row>
@@ -3818,17 +3818,17 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I72" s="2" t="n">
         <v>8</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-08-04 23:27:40</t>
+          <t>2026-09-14 19:13:34</t>
         </is>
       </c>
     </row>
@@ -3864,17 +3864,17 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>1415</v>
+        <v>1441</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>20</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-08-04 23:27:55</t>
+          <t>2026-09-14 19:13:42</t>
         </is>
       </c>
     </row>
@@ -3910,17 +3910,17 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>345</v>
+        <v>362</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>10</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-08-04 23:28:05</t>
+          <t>2026-09-14 19:13:48</t>
         </is>
       </c>
     </row>
@@ -3956,17 +3956,17 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>1320</v>
+        <v>1360</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-08-04 23:28:18</t>
+          <t>2026-09-14 19:13:54</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>1587</v>
+        <v>1614</v>
       </c>
       <c r="H76" s="2" t="n">
         <v>17</v>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-08-04 23:28:24</t>
+          <t>2026-09-14 19:14:08</t>
         </is>
       </c>
     </row>
@@ -4048,17 +4048,17 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>4483</v>
+        <v>4556</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I77" s="2" t="n">
         <v>64</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-08-04 23:28:34</t>
+          <t>2026-09-14 19:14:20</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>739</v>
+        <v>753</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>14</v>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-08-04 23:28:45</t>
+          <t>2026-09-14 19:14:28</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-08-04 23:29:00</t>
+          <t>2026-09-14 19:14:33</t>
         </is>
       </c>
     </row>
@@ -4186,17 +4186,17 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>637</v>
+        <v>682</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I80" s="2" t="n">
         <v>15</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-08-04 23:29:07</t>
+          <t>2026-09-14 19:14:41</t>
         </is>
       </c>
     </row>
@@ -4232,17 +4232,17 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>1395</v>
+        <v>1423</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I81" s="2" t="n">
         <v>24</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-08-04 23:29:17</t>
+          <t>2026-09-14 19:14:49</t>
         </is>
       </c>
     </row>
@@ -4278,17 +4278,17 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>3540</v>
+        <v>3652</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I82" s="2" t="n">
         <v>57</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-08-04 23:29:29</t>
+          <t>2026-09-14 19:14:59</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4324,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>727</v>
+        <v>762</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>15</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-08-04 23:29:34</t>
+          <t>2026-09-14 19:15:05</t>
         </is>
       </c>
     </row>
@@ -4370,17 +4370,17 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>5</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-08-04 23:29:46</t>
+          <t>2026-09-14 19:15:11</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>971</v>
+        <v>988</v>
       </c>
       <c r="H85" s="2" t="n">
         <v>13</v>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-08-04 23:29:55</t>
+          <t>2026-09-14 19:15:19</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4462,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>781</v>
+        <v>812</v>
       </c>
       <c r="H86" s="2" t="n">
         <v>15</v>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-08-04 23:30:07</t>
+          <t>2026-09-14 19:15:29</t>
         </is>
       </c>
     </row>
@@ -4508,17 +4508,17 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>712</v>
+        <v>742</v>
       </c>
       <c r="H87" s="2" t="n">
         <v>15</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-08-04 23:30:21</t>
+          <t>2026-09-14 19:15:39</t>
         </is>
       </c>
     </row>
@@ -4554,17 +4554,17 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>548</v>
+        <v>577</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-08-04 23:30:31</t>
+          <t>2026-09-14 19:15:53</t>
         </is>
       </c>
     </row>
@@ -4641,17 +4641,17 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>3106</v>
+        <v>3209</v>
       </c>
       <c r="H90" s="2" t="n">
         <v>32</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-08-04 23:31:14</t>
+          <t>2026-09-14 19:16:32</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>498</v>
+        <v>514</v>
       </c>
       <c r="H91" s="2" t="n">
         <v>12</v>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-08-04 23:31:29</t>
+          <t>2026-09-14 19:16:45</t>
         </is>
       </c>
     </row>
@@ -4733,17 +4733,17 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>2411</v>
+        <v>2463</v>
       </c>
       <c r="H92" s="2" t="n">
         <v>22</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-08-04 23:31:42</t>
+          <t>2026-09-14 19:16:51</t>
         </is>
       </c>
     </row>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>1372</v>
+        <v>1397</v>
       </c>
       <c r="H93" s="2" t="n">
         <v>19</v>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-08-04 23:31:54</t>
+          <t>2026-09-14 19:16:59</t>
         </is>
       </c>
     </row>

--- a/New Google Scholar List.xlsx
+++ b/New Google Scholar List.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="60" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$I$109</definedName>
@@ -609,17 +609,17 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1455</v>
+        <v>1387</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>2026-09-14 19:02:16</t>
+          <t>2026-08-04 23:15:29</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>737</v>
+        <v>695</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>16</v>
@@ -665,7 +665,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-14 19:02:29</t>
+          <t>2026-08-04 23:15:43</t>
         </is>
       </c>
     </row>
@@ -701,17 +701,17 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>6333</v>
+        <v>6127</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-14 19:02:38</t>
+          <t>2026-08-04 23:15:51</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>2148</v>
+        <v>2106</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>21</v>
@@ -757,7 +757,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-14 19:02:48</t>
+          <t>2026-08-04 23:16:03</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1494</v>
+        <v>1453</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>20</v>
@@ -803,7 +803,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-14 19:03:00</t>
+          <t>2026-08-04 23:16:12</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>563</v>
+        <v>540</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>15</v>
@@ -849,7 +849,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-14 19:03:12</t>
+          <t>2026-08-04 23:16:22</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1468</v>
+        <v>1399</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>14</v>
@@ -895,7 +895,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-14 19:03:24</t>
+          <t>2026-08-04 23:16:30</t>
         </is>
       </c>
     </row>
@@ -931,17 +931,17 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-14 19:03:31</t>
+          <t>2026-08-04 23:16:38</t>
         </is>
       </c>
     </row>
@@ -977,17 +977,17 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>871</v>
+        <v>844</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-14 19:03:46</t>
+          <t>2026-08-04 23:16:49</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>712</v>
+        <v>695</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>14</v>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-14 19:04:00</t>
+          <t>2026-08-04 23:17:02</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>380</v>
+        <v>353</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>6</v>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-14 19:04:12</t>
+          <t>2026-08-04 23:17:11</t>
         </is>
       </c>
     </row>
@@ -1115,17 +1115,17 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1931</v>
+        <v>1896</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>38</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-14 19:04:22</t>
+          <t>2026-08-04 23:17:25</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>4</v>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-14 19:04:35</t>
+          <t>2026-08-04 23:17:39</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I15" s="2" t="n">
         <v>7</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-14 19:04:44</t>
+          <t>2026-08-04 23:17:47</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>795</v>
+        <v>767</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>15</v>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-14 19:04:55</t>
+          <t>2026-08-04 23:17:57</t>
         </is>
       </c>
     </row>
@@ -1299,17 +1299,17 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>6</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-14 19:05:10</t>
+          <t>2026-08-04 23:18:07</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>5</v>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-14 19:05:18</t>
+          <t>2026-08-04 23:18:19</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>7</v>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-14 19:05:24</t>
+          <t>2026-08-04 23:18:30</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>4</v>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-14 19:05:32</t>
+          <t>2026-08-04 23:18:44</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1871</v>
+        <v>1746</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-09-14 19:05:40</t>
+          <t>2026-08-04 23:18:56</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1515</v>
+        <v>1480</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>23</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-09-14 19:05:45</t>
+          <t>2026-08-04 23:19:10</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>1446</v>
+        <v>1418</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>20</v>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-09-14 19:05:57</t>
+          <t>2026-08-04 23:19:21</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>1446</v>
+        <v>1418</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>20</v>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-09-14 19:06:06</t>
+          <t>2026-08-04 23:19:26</t>
         </is>
       </c>
     </row>
@@ -1667,17 +1667,17 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>707</v>
+        <v>676</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>14</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-09-14 19:06:13</t>
+          <t>2026-08-04 23:19:34</t>
         </is>
       </c>
     </row>
@@ -1713,17 +1713,17 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>1894</v>
+        <v>1852</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I26" s="2" t="n">
         <v>36</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-09-14 19:06:24</t>
+          <t>2026-08-04 23:19:48</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>12</v>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-09-14 19:06:35</t>
+          <t>2026-08-04 23:20:02</t>
         </is>
       </c>
     </row>
@@ -1805,17 +1805,17 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>1947</v>
+        <v>1878</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-09-14 19:06:41</t>
+          <t>2026-08-04 23:20:12</t>
         </is>
       </c>
     </row>
@@ -1851,17 +1851,17 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>1334</v>
+        <v>1301</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-09-14 19:06:48</t>
+          <t>2026-08-04 23:20:20</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>635</v>
+        <v>606</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>11</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-09-14 19:06:59</t>
+          <t>2026-08-04 23:20:28</t>
         </is>
       </c>
     </row>
@@ -1943,17 +1943,17 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>3057</v>
+        <v>2962</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-09-14 19:07:05</t>
+          <t>2026-08-04 23:20:33</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-09-14 19:07:14</t>
+          <t>2026-08-04 23:20:47</t>
         </is>
       </c>
     </row>
@@ -2035,17 +2035,17 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>7</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-09-14 19:07:28</t>
+          <t>2026-08-04 23:21:00</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>1033</v>
+        <v>1001</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>15</v>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-09-14 19:07:34</t>
+          <t>2026-08-04 23:21:13</t>
         </is>
       </c>
     </row>
@@ -2127,17 +2127,17 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>1573</v>
+        <v>1541</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>21</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-09-14 19:07:42</t>
+          <t>2026-08-04 23:21:21</t>
         </is>
       </c>
     </row>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>10</v>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-09-14 19:07:50</t>
+          <t>2026-08-04 23:21:34</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>1495</v>
+        <v>1457</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>17</v>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-09-14 19:07:59</t>
+          <t>2026-08-04 23:21:47</t>
         </is>
       </c>
     </row>
@@ -2265,17 +2265,17 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>1642</v>
+        <v>1580</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>18</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-09-14 19:08:07</t>
+          <t>2026-08-04 23:22:01</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>12</v>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-09-14 19:08:21</t>
+          <t>2026-08-04 23:22:16</t>
         </is>
       </c>
     </row>
@@ -2357,17 +2357,17 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>3854</v>
+        <v>3758</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-09-14 19:08:28</t>
+          <t>2026-08-04 23:22:25</t>
         </is>
       </c>
     </row>
@@ -2403,17 +2403,17 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>3274</v>
+        <v>3116</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>28</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-09-14 19:08:42</t>
+          <t>2026-08-04 23:22:38</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>720</v>
+        <v>693</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>13</v>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-09-14 19:08:53</t>
+          <t>2026-08-04 23:22:45</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>9</v>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-09-14 19:09:07</t>
+          <t>2026-08-04 23:22:53</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>461</v>
+        <v>445</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>10</v>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-09-14 19:09:17</t>
+          <t>2026-08-04 23:23:07</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-09-14 19:09:25</t>
+          <t>2026-08-04 23:23:18</t>
         </is>
       </c>
     </row>
@@ -2668,17 +2668,17 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>2355</v>
+        <v>2268</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-09-14 19:09:31</t>
+          <t>2026-08-04 23:23:25</t>
         </is>
       </c>
     </row>
@@ -2714,17 +2714,17 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>2319</v>
+        <v>2259</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>28</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-09-14 19:09:44</t>
+          <t>2026-08-04 23:23:38</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>1254</v>
+        <v>1205</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>17</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-09-14 19:09:52</t>
+          <t>2026-08-04 23:23:52</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>7</v>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-09-14 19:09:58</t>
+          <t>2026-08-04 23:23:57</t>
         </is>
       </c>
     </row>
@@ -2852,17 +2852,17 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I51" s="2" t="n">
         <v>3</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-09-14 19:10:04</t>
+          <t>2026-08-04 23:24:04</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>1114</v>
+        <v>1046</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>13</v>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-09-14 19:10:13</t>
+          <t>2026-08-04 23:24:17</t>
         </is>
       </c>
     </row>
@@ -2944,17 +2944,17 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>2940</v>
+        <v>2837</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-09-14 19:10:19</t>
+          <t>2026-08-04 23:24:26</t>
         </is>
       </c>
     </row>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>4500</v>
+        <v>4394</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>37</v>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-09-14 19:10:29</t>
+          <t>2026-08-04 23:24:33</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>6</v>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-09-14 19:10:35</t>
+          <t>2026-08-04 23:24:45</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>7</v>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-09-14 19:10:45</t>
+          <t>2026-08-04 23:24:55</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>2</v>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-09-14 19:10:53</t>
+          <t>2026-08-04 23:25:01</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>1985</v>
+        <v>1933</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>22</v>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-09-14 19:11:08</t>
+          <t>2026-08-04 23:25:09</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>525</v>
+        <v>509</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>12</v>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-09-14 19:11:16</t>
+          <t>2026-08-04 23:25:20</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>1077</v>
+        <v>1023</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>17</v>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-09-14 19:11:23</t>
+          <t>2026-08-04 23:25:30</t>
         </is>
       </c>
     </row>
@@ -3312,17 +3312,17 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>2301</v>
+        <v>2226</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-09-14 19:11:29</t>
+          <t>2026-08-04 23:25:40</t>
         </is>
       </c>
     </row>
@@ -3358,17 +3358,17 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>1580</v>
+        <v>1547</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>22</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-09-14 19:11:42</t>
+          <t>2026-08-04 23:25:46</t>
         </is>
       </c>
     </row>
@@ -3404,17 +3404,17 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>1214</v>
+        <v>1170</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-09-14 19:11:50</t>
+          <t>2026-08-04 23:25:58</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>9</v>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-09-14 19:12:05</t>
+          <t>2026-08-04 23:26:08</t>
         </is>
       </c>
     </row>
@@ -3496,17 +3496,17 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>7441</v>
+        <v>7256</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-09-14 19:12:19</t>
+          <t>2026-08-04 23:26:20</t>
         </is>
       </c>
     </row>
@@ -3542,17 +3542,17 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>1310</v>
+        <v>1262</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>19</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-09-14 19:12:31</t>
+          <t>2026-08-04 23:26:26</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>2244</v>
+        <v>2190</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>28</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-09-14 19:12:42</t>
+          <t>2026-08-04 23:26:41</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3634,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>8</v>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-09-14 19:12:55</t>
+          <t>2026-08-04 23:26:54</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>555</v>
+        <v>536</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>11</v>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-09-14 19:13:08</t>
+          <t>2026-08-04 23:27:06</t>
         </is>
       </c>
     </row>
@@ -3726,17 +3726,17 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>520</v>
+        <v>502</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>11</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-09-14 19:13:18</t>
+          <t>2026-08-04 23:27:17</t>
         </is>
       </c>
     </row>
@@ -3772,17 +3772,17 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>4208</v>
+        <v>4058</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-09-14 19:13:24</t>
+          <t>2026-08-04 23:27:26</t>
         </is>
       </c>
     </row>
@@ -3818,17 +3818,17 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I72" s="2" t="n">
         <v>8</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-09-14 19:13:34</t>
+          <t>2026-08-04 23:27:40</t>
         </is>
       </c>
     </row>
@@ -3864,17 +3864,17 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>1441</v>
+        <v>1415</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>20</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-09-14 19:13:42</t>
+          <t>2026-08-04 23:27:55</t>
         </is>
       </c>
     </row>
@@ -3910,17 +3910,17 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>10</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-09-14 19:13:48</t>
+          <t>2026-08-04 23:28:05</t>
         </is>
       </c>
     </row>
@@ -3956,17 +3956,17 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>1360</v>
+        <v>1320</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-09-14 19:13:54</t>
+          <t>2026-08-04 23:28:18</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>1614</v>
+        <v>1587</v>
       </c>
       <c r="H76" s="2" t="n">
         <v>17</v>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-09-14 19:14:08</t>
+          <t>2026-08-04 23:28:24</t>
         </is>
       </c>
     </row>
@@ -4048,17 +4048,17 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>4556</v>
+        <v>4483</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I77" s="2" t="n">
         <v>64</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-09-14 19:14:20</t>
+          <t>2026-08-04 23:28:34</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>753</v>
+        <v>739</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>14</v>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-09-14 19:14:28</t>
+          <t>2026-08-04 23:28:45</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-09-14 19:14:33</t>
+          <t>2026-08-04 23:29:00</t>
         </is>
       </c>
     </row>
@@ -4186,17 +4186,17 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>682</v>
+        <v>637</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I80" s="2" t="n">
         <v>15</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-09-14 19:14:41</t>
+          <t>2026-08-04 23:29:07</t>
         </is>
       </c>
     </row>
@@ -4232,17 +4232,17 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>1423</v>
+        <v>1395</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I81" s="2" t="n">
         <v>24</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-09-14 19:14:49</t>
+          <t>2026-08-04 23:29:17</t>
         </is>
       </c>
     </row>
@@ -4278,17 +4278,17 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>3652</v>
+        <v>3540</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I82" s="2" t="n">
         <v>57</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-09-14 19:14:59</t>
+          <t>2026-08-04 23:29:29</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4324,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>762</v>
+        <v>727</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>15</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:05</t>
+          <t>2026-08-04 23:29:34</t>
         </is>
       </c>
     </row>
@@ -4370,17 +4370,17 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>5</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:11</t>
+          <t>2026-08-04 23:29:46</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>988</v>
+        <v>971</v>
       </c>
       <c r="H85" s="2" t="n">
         <v>13</v>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:19</t>
+          <t>2026-08-04 23:29:55</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4462,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>812</v>
+        <v>781</v>
       </c>
       <c r="H86" s="2" t="n">
         <v>15</v>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:29</t>
+          <t>2026-08-04 23:30:07</t>
         </is>
       </c>
     </row>
@@ -4508,17 +4508,17 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>742</v>
+        <v>712</v>
       </c>
       <c r="H87" s="2" t="n">
         <v>15</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:39</t>
+          <t>2026-08-04 23:30:21</t>
         </is>
       </c>
     </row>
@@ -4554,17 +4554,17 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>577</v>
+        <v>548</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-09-14 19:15:53</t>
+          <t>2026-08-04 23:30:31</t>
         </is>
       </c>
     </row>
@@ -4641,17 +4641,17 @@
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>3209</v>
+        <v>3106</v>
       </c>
       <c r="H90" s="2" t="n">
         <v>32</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-09-14 19:16:32</t>
+          <t>2026-08-04 23:31:14</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>514</v>
+        <v>498</v>
       </c>
       <c r="H91" s="2" t="n">
         <v>12</v>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-09-14 19:16:45</t>
+          <t>2026-08-04 23:31:29</t>
         </is>
       </c>
     </row>
@@ -4733,17 +4733,17 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>2463</v>
+        <v>2411</v>
       </c>
       <c r="H92" s="2" t="n">
         <v>22</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-09-14 19:16:51</t>
+          <t>2026-08-04 23:31:42</t>
         </is>
       </c>
     </row>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>1397</v>
+        <v>1372</v>
       </c>
       <c r="H93" s="2" t="n">
         <v>19</v>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-09-14 19:16:59</t>
+          <t>2026-08-04 23:31:54</t>
         </is>
       </c>
     </row>

--- a/New Google Scholar List.xlsx
+++ b/New Google Scholar List.xlsx
@@ -512,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K93"/>
+  <dimension ref="A1:N93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="15.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -556,22 +556,37 @@
           <t>Link to Google Scholar Profile</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Citations (All)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>h-index (All)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>i10-index (All)</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>Citations (Since 2021)</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>h-index (Since 2021)</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>i10-index (Since 2021)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Last Updated</t>
         </is>
@@ -608,18 +623,27 @@
           <t>https://scholar.google.com/citations?hl=en&amp;user=zxokCVwAAAAJ&amp;view_op=list_works&amp;sortby=pubdate</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n">
-        <v>1387</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:15:29</t>
+      <c r="G2" t="n">
+        <v>1564</v>
+      </c>
+      <c r="H2" t="n">
+        <v>17</v>
+      </c>
+      <c r="I2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>1460</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:46:06</t>
         </is>
       </c>
     </row>
@@ -654,18 +678,27 @@
           <t>https://scholar.google.com/citations?user=Q-givk4AAAAJ&amp;hl=en</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n">
-        <v>695</v>
-      </c>
-      <c r="H3" s="2" t="n">
+      <c r="G3" t="n">
+        <v>821</v>
+      </c>
+      <c r="H3" t="n">
         <v>16</v>
       </c>
-      <c r="I3" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:15:43</t>
+      <c r="I3" t="n">
+        <v>21</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>739</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:46:10</t>
         </is>
       </c>
     </row>
@@ -700,18 +733,27 @@
           <t>https://scholar.google.com/citations?user=qUomLPAAAAAJ&amp;hl=en&amp;oi=sra</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n">
-        <v>6127</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>113</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:15:51</t>
+      <c r="G4" t="n">
+        <v>8423</v>
+      </c>
+      <c r="H4" t="n">
+        <v>49</v>
+      </c>
+      <c r="I4" t="n">
+        <v>127</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>6343</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:46:16</t>
         </is>
       </c>
     </row>
@@ -746,18 +788,27 @@
           <t>https://scholar.google.com/citations?user=zGMb2OcAAAAJ&amp;hl=en&amp;oi=ao</t>
         </is>
       </c>
-      <c r="G5" s="2" t="n">
-        <v>2106</v>
-      </c>
-      <c r="H5" s="2" t="n">
+      <c r="G5" t="n">
+        <v>6566</v>
+      </c>
+      <c r="H5" t="n">
+        <v>38</v>
+      </c>
+      <c r="I5" t="n">
+        <v>99</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>2149</v>
+      </c>
+      <c r="K5" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="L5" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:16:03</t>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:48:07</t>
         </is>
       </c>
     </row>
@@ -792,18 +843,27 @@
           <t>https://scholar.google.com/citations?hl=en&amp;user=n4TqYW4AAAAJ&amp;view_op=list_works&amp;sortby=pubdate</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n">
-        <v>1453</v>
-      </c>
-      <c r="H6" s="2" t="n">
+      <c r="G6" t="n">
+        <v>4885</v>
+      </c>
+      <c r="H6" t="n">
+        <v>32</v>
+      </c>
+      <c r="I6" t="n">
+        <v>58</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>1496</v>
+      </c>
+      <c r="K6" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="L6" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:16:12</t>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:48:20</t>
         </is>
       </c>
     </row>
@@ -838,18 +898,27 @@
           <t>https://scholar.google.com/citations?user=7cDhJxoAAAAJ</t>
         </is>
       </c>
-      <c r="G7" s="2" t="n">
-        <v>540</v>
-      </c>
-      <c r="H7" s="2" t="n">
+      <c r="G7" t="n">
+        <v>886</v>
+      </c>
+      <c r="H7" t="n">
+        <v>18</v>
+      </c>
+      <c r="I7" t="n">
+        <v>22</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>564</v>
+      </c>
+      <c r="K7" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="L7" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:16:22</t>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:48:33</t>
         </is>
       </c>
     </row>
@@ -884,18 +953,27 @@
           <t xml:space="preserve">https://scholar.google.com/citations?hl=en&amp;user=pAk1jSAAAAAJ&amp;view_op=list_works&amp;sortby=pubdate </t>
         </is>
       </c>
-      <c r="G8" s="2" t="n">
-        <v>1399</v>
-      </c>
-      <c r="H8" s="2" t="n">
+      <c r="G8" t="n">
+        <v>1504</v>
+      </c>
+      <c r="H8" t="n">
+        <v>15</v>
+      </c>
+      <c r="I8" t="n">
+        <v>19</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>1469</v>
+      </c>
+      <c r="K8" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="L8" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:16:30</t>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:48:41</t>
         </is>
       </c>
     </row>
@@ -930,18 +1008,27 @@
           <t>https://scholar.google.com/citations?hl=en&amp;user=TmeTV7IAAAAJ</t>
         </is>
       </c>
-      <c r="G9" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:16:38</t>
+      <c r="G9" t="n">
+        <v>76</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:48:53</t>
         </is>
       </c>
     </row>
@@ -976,18 +1063,27 @@
           <t>https://scholar.google.com/citations?user=wCX7WSMAAAAJ&amp;hl=en</t>
         </is>
       </c>
-      <c r="G10" s="2" t="n">
-        <v>844</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:16:49</t>
+      <c r="G10" t="n">
+        <v>2009</v>
+      </c>
+      <c r="H10" t="n">
+        <v>16</v>
+      </c>
+      <c r="I10" t="n">
+        <v>29</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>871</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:49:02</t>
         </is>
       </c>
     </row>
@@ -1022,18 +1118,27 @@
           <t>https://scholar.google.com/citations?hl=en&amp;user=vz9tFy4AAAAJ</t>
         </is>
       </c>
-      <c r="G11" s="2" t="n">
-        <v>695</v>
-      </c>
-      <c r="H11" s="2" t="n">
+      <c r="G11" t="n">
+        <v>977</v>
+      </c>
+      <c r="H11" t="n">
+        <v>16</v>
+      </c>
+      <c r="I11" t="n">
+        <v>23</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>714</v>
+      </c>
+      <c r="K11" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="I11" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:17:02</t>
+      <c r="L11" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:49:10</t>
         </is>
       </c>
     </row>
@@ -1068,18 +1173,27 @@
           <t xml:space="preserve">https://scholar.google.com/citations?user=b41dGVUAAAAJ&amp;hl=en </t>
         </is>
       </c>
-      <c r="G12" s="2" t="n">
-        <v>353</v>
-      </c>
-      <c r="H12" s="2" t="n">
+      <c r="G12" t="n">
+        <v>408</v>
+      </c>
+      <c r="H12" t="n">
         <v>6</v>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="I12" t="n">
         <v>6</v>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:17:11</t>
+      <c r="J12" s="2" t="n">
+        <v>380</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:49:16</t>
         </is>
       </c>
     </row>
@@ -1114,18 +1228,27 @@
           <t>https://scholar.google.com/citations?user=0auA760AAAAJ&amp;hl=en&amp;oi=ao</t>
         </is>
       </c>
-      <c r="G13" s="2" t="n">
-        <v>1896</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="I13" s="2" t="n">
+      <c r="G13" t="n">
+        <v>6610</v>
+      </c>
+      <c r="H13" t="n">
+        <v>40</v>
+      </c>
+      <c r="I13" t="n">
+        <v>76</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>1931</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="L13" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:17:25</t>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:49:25</t>
         </is>
       </c>
     </row>
@@ -1160,18 +1283,27 @@
           <t>https://scholar.google.com/citations?hl=en&amp;user=aS7n-uIAAAAJ</t>
         </is>
       </c>
-      <c r="G14" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="H14" s="2" t="n">
+      <c r="G14" t="n">
+        <v>202</v>
+      </c>
+      <c r="H14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I14" t="n">
+        <v>6</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="K14" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="L14" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:17:39</t>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:49:33</t>
         </is>
       </c>
     </row>
@@ -1206,18 +1338,27 @@
           <t>https://scholar.google.com/citations?hl=en&amp;user=uvhrXE4AAAAJ</t>
         </is>
       </c>
-      <c r="G15" s="2" t="n">
-        <v>380</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="I15" s="2" t="n">
+      <c r="G15" t="n">
+        <v>551</v>
+      </c>
+      <c r="H15" t="n">
+        <v>13</v>
+      </c>
+      <c r="I15" t="n">
+        <v>14</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>395</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="L15" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:17:47</t>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:49:44</t>
         </is>
       </c>
     </row>
@@ -1252,18 +1393,27 @@
           <t>https://scholar.google.com/citations?user=HLJlITsAAAAJ&amp;hl=en&amp;oi=ao</t>
         </is>
       </c>
-      <c r="G16" s="2" t="n">
-        <v>767</v>
-      </c>
-      <c r="H16" s="2" t="n">
+      <c r="G16" t="n">
+        <v>1435</v>
+      </c>
+      <c r="H16" t="n">
+        <v>20</v>
+      </c>
+      <c r="I16" t="n">
+        <v>51</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>795</v>
+      </c>
+      <c r="K16" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="I16" s="2" t="n">
+      <c r="L16" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:17:57</t>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:49:51</t>
         </is>
       </c>
     </row>
@@ -1298,18 +1448,27 @@
           <t xml:space="preserve">https://scholar.google.com/citations?user=pBjLQFUAAAAJ&amp;hl=en </t>
         </is>
       </c>
-      <c r="G17" s="2" t="n">
-        <v>108</v>
-      </c>
-      <c r="H17" s="2" t="n">
+      <c r="G17" t="n">
+        <v>114</v>
+      </c>
+      <c r="H17" t="n">
         <v>6</v>
       </c>
-      <c r="I17" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:18:07</t>
+      <c r="I17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:50:02</t>
         </is>
       </c>
     </row>
@@ -1344,18 +1503,27 @@
           <t>https://scholar.google.com/citations?hl=&amp;user=VIhfMWYAAAAJ</t>
         </is>
       </c>
-      <c r="G18" s="2" t="n">
-        <v>85</v>
-      </c>
-      <c r="H18" s="2" t="n">
+      <c r="G18" t="n">
+        <v>122</v>
+      </c>
+      <c r="H18" t="n">
         <v>5</v>
       </c>
-      <c r="I18" s="2" t="n">
+      <c r="I18" t="n">
         <v>3</v>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:18:19</t>
+      <c r="J18" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:50:08</t>
         </is>
       </c>
     </row>
@@ -1390,18 +1558,27 @@
           <t xml:space="preserve">https://scholar.google.com/citations?user=lsCjJTgAAAAJ&amp;hl=en </t>
         </is>
       </c>
-      <c r="G19" s="2" t="n">
-        <v>254</v>
-      </c>
-      <c r="H19" s="2" t="n">
+      <c r="G19" t="n">
+        <v>360</v>
+      </c>
+      <c r="H19" t="n">
         <v>7</v>
       </c>
-      <c r="I19" s="2" t="n">
+      <c r="I19" t="n">
         <v>7</v>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:18:30</t>
+      <c r="J19" s="2" t="n">
+        <v>268</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:50:16</t>
         </is>
       </c>
     </row>
@@ -1436,18 +1613,27 @@
           <t>https://scholar.google.com/citations?user=_KY1q1AAAAAJ&amp;hl=en&amp;oi=ao</t>
         </is>
       </c>
-      <c r="G20" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="H20" s="2" t="n">
+      <c r="G20" t="n">
+        <v>133</v>
+      </c>
+      <c r="H20" t="n">
+        <v>6</v>
+      </c>
+      <c r="I20" t="n">
+        <v>5</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="K20" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I20" s="2" t="n">
+      <c r="L20" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:18:44</t>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:50:21</t>
         </is>
       </c>
     </row>
@@ -1482,18 +1668,27 @@
           <t>https://scholar.google.com/citations?user=Glce_CEAAAAJ&amp;hl=en&amp;oi=ao</t>
         </is>
       </c>
-      <c r="G21" s="2" t="n">
-        <v>1746</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:18:56</t>
+      <c r="G21" t="n">
+        <v>5708</v>
+      </c>
+      <c r="H21" t="n">
+        <v>34</v>
+      </c>
+      <c r="I21" t="n">
+        <v>87</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>1874</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:50:28</t>
         </is>
       </c>
     </row>
@@ -1528,18 +1723,27 @@
           <t>https://scholar.google.com/citations?user=mpd4yWsAAAAJ&amp;hl=en&amp;oi=sra</t>
         </is>
       </c>
-      <c r="G22" s="2" t="n">
-        <v>1480</v>
-      </c>
-      <c r="H22" s="2" t="n">
+      <c r="G22" t="n">
+        <v>3703</v>
+      </c>
+      <c r="H22" t="n">
+        <v>35</v>
+      </c>
+      <c r="I22" t="n">
+        <v>57</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>1516</v>
+      </c>
+      <c r="K22" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="I22" s="2" t="n">
+      <c r="L22" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:19:10</t>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:50:40</t>
         </is>
       </c>
     </row>
@@ -1574,18 +1778,27 @@
           <t>https://scholar.google.com/citations?user=jd3wW3gAAAAJ&amp;hl=en&amp;oi=ao</t>
         </is>
       </c>
-      <c r="G23" s="2" t="n">
-        <v>1418</v>
-      </c>
-      <c r="H23" s="2" t="n">
+      <c r="G23" t="n">
+        <v>3155</v>
+      </c>
+      <c r="H23" t="n">
+        <v>29</v>
+      </c>
+      <c r="I23" t="n">
+        <v>47</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>1447</v>
+      </c>
+      <c r="K23" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="I23" s="2" t="n">
+      <c r="L23" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:19:21</t>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:50:50</t>
         </is>
       </c>
     </row>
@@ -1620,18 +1833,27 @@
           <t>https://scholar.google.com/citations?user=jd3wW3gAAAAJ&amp;hl=en&amp;oi=ao</t>
         </is>
       </c>
-      <c r="G24" s="2" t="n">
-        <v>1418</v>
-      </c>
-      <c r="H24" s="2" t="n">
+      <c r="G24" t="n">
+        <v>3155</v>
+      </c>
+      <c r="H24" t="n">
+        <v>29</v>
+      </c>
+      <c r="I24" t="n">
+        <v>47</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>1447</v>
+      </c>
+      <c r="K24" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="I24" s="2" t="n">
+      <c r="L24" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:19:26</t>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:50:58</t>
         </is>
       </c>
     </row>
@@ -1666,18 +1888,27 @@
           <t>https://scholar.google.com/citations?user=bqYZ2mYAAAAJ&amp;hl=en&amp;oi=ao</t>
         </is>
       </c>
-      <c r="G25" s="2" t="n">
-        <v>676</v>
-      </c>
-      <c r="H25" s="2" t="n">
+      <c r="G25" t="n">
+        <v>1938</v>
+      </c>
+      <c r="H25" t="n">
+        <v>23</v>
+      </c>
+      <c r="I25" t="n">
+        <v>68</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>707</v>
+      </c>
+      <c r="K25" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="I25" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:19:34</t>
+      <c r="L25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:51:11</t>
         </is>
       </c>
     </row>
@@ -1712,18 +1943,27 @@
           <t>https://scholar.google.com/citations?user=EPtQbdUAAAAJ&amp;hl=en&amp;oi=ao</t>
         </is>
       </c>
-      <c r="G26" s="2" t="n">
-        <v>1852</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="I26" s="2" t="n">
+      <c r="G26" t="n">
+        <v>2895</v>
+      </c>
+      <c r="H26" t="n">
+        <v>29</v>
+      </c>
+      <c r="I26" t="n">
+        <v>40</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>1893</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="L26" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:19:48</t>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:51:19</t>
         </is>
       </c>
     </row>
@@ -1758,18 +1998,27 @@
           <t>https://scholar.google.com/citations?hl=en&amp;user=4oVa-uQAAAAJ</t>
         </is>
       </c>
-      <c r="G27" s="2" t="n">
-        <v>425</v>
-      </c>
-      <c r="H27" s="2" t="n">
+      <c r="G27" t="n">
+        <v>1678</v>
+      </c>
+      <c r="H27" t="n">
+        <v>18</v>
+      </c>
+      <c r="I27" t="n">
+        <v>23</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>437</v>
+      </c>
+      <c r="K27" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="I27" s="2" t="n">
+      <c r="L27" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:20:02</t>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:51:34</t>
         </is>
       </c>
     </row>
@@ -1804,18 +2053,27 @@
           <t>https://scholar.google.com/citations?user=nd2WEc0AAAAJ&amp;hl=en&amp;oi=ao</t>
         </is>
       </c>
-      <c r="G28" s="2" t="n">
-        <v>1878</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:20:12</t>
+      <c r="G28" t="n">
+        <v>2641</v>
+      </c>
+      <c r="H28" t="n">
+        <v>23</v>
+      </c>
+      <c r="I28" t="n">
+        <v>42</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>1948</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:51:47</t>
         </is>
       </c>
     </row>
@@ -1850,18 +2108,27 @@
           <t>https://scholar.google.com/citations?user=NksdIW0AAAAJ&amp;hl=en&amp;oi=ao</t>
         </is>
       </c>
-      <c r="G29" s="2" t="n">
-        <v>1301</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:20:20</t>
+      <c r="G29" t="n">
+        <v>2956</v>
+      </c>
+      <c r="H29" t="n">
+        <v>32</v>
+      </c>
+      <c r="I29" t="n">
+        <v>60</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>1334</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:51:59</t>
         </is>
       </c>
     </row>
@@ -1896,18 +2163,27 @@
           <t xml:space="preserve">https://scholar.google.com/citations?user=Lbz_9NUAAAAJ&amp;hl=en </t>
         </is>
       </c>
-      <c r="G30" s="2" t="n">
-        <v>606</v>
-      </c>
-      <c r="H30" s="2" t="n">
+      <c r="G30" t="n">
+        <v>856</v>
+      </c>
+      <c r="H30" t="n">
+        <v>12</v>
+      </c>
+      <c r="I30" t="n">
+        <v>13</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>636</v>
+      </c>
+      <c r="K30" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="I30" s="2" t="n">
+      <c r="L30" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:20:28</t>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:52:13</t>
         </is>
       </c>
     </row>
@@ -1942,18 +2218,27 @@
           <t>https://scholar.google.com/citations?user=rjPbFYgAAAAJ&amp;hl=en&amp;oi=ao</t>
         </is>
       </c>
-      <c r="G31" s="2" t="n">
-        <v>2962</v>
-      </c>
-      <c r="H31" s="2" t="n">
+      <c r="G31" t="n">
+        <v>9154</v>
+      </c>
+      <c r="H31" t="n">
+        <v>46</v>
+      </c>
+      <c r="I31" t="n">
+        <v>108</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>3057</v>
+      </c>
+      <c r="K31" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="I31" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:20:33</t>
+      <c r="L31" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:52:20</t>
         </is>
       </c>
     </row>
@@ -1988,18 +2273,27 @@
           <t>https://scholar.google.com/citations?user=j2JncDAAAAAJ&amp;hl=en</t>
         </is>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="G32" t="n">
+        <v>41</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2</v>
+      </c>
+      <c r="J32" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="H32" s="2" t="n">
+      <c r="K32" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="I32" s="2" t="n">
+      <c r="L32" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:20:47</t>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:52:28</t>
         </is>
       </c>
     </row>
@@ -2034,18 +2328,27 @@
           <t>https://scholar.google.com/citations?user=SEqUzPQAAAAJ&amp;hl=en</t>
         </is>
       </c>
-      <c r="G33" s="2" t="n">
-        <v>159</v>
-      </c>
-      <c r="H33" s="2" t="n">
+      <c r="G33" t="n">
+        <v>301</v>
+      </c>
+      <c r="H33" t="n">
+        <v>10</v>
+      </c>
+      <c r="I33" t="n">
+        <v>11</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>162</v>
+      </c>
+      <c r="K33" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="I33" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:21:00</t>
+      <c r="L33" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:52:39</t>
         </is>
       </c>
     </row>
@@ -2080,18 +2383,27 @@
           <t>https://scholar.google.com/citations?hl=en&amp;user=ai_6D40AAAAJ</t>
         </is>
       </c>
-      <c r="G34" s="2" t="n">
-        <v>1001</v>
-      </c>
-      <c r="H34" s="2" t="n">
+      <c r="G34" t="n">
+        <v>1268</v>
+      </c>
+      <c r="H34" t="n">
+        <v>18</v>
+      </c>
+      <c r="I34" t="n">
+        <v>26</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>1035</v>
+      </c>
+      <c r="K34" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="I34" s="2" t="n">
+      <c r="L34" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:21:13</t>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:52:50</t>
         </is>
       </c>
     </row>
@@ -2126,18 +2438,27 @@
           <t>https://scholar.google.com/citations?user=XyHzOmgAAAAJ&amp;hl=en</t>
         </is>
       </c>
-      <c r="G35" s="2" t="n">
-        <v>1541</v>
-      </c>
-      <c r="H35" s="2" t="n">
+      <c r="G35" t="n">
+        <v>3496</v>
+      </c>
+      <c r="H35" t="n">
+        <v>32</v>
+      </c>
+      <c r="I35" t="n">
+        <v>60</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>1574</v>
+      </c>
+      <c r="K35" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="I35" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:21:21</t>
+      <c r="L35" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:53:05</t>
         </is>
       </c>
     </row>
@@ -2172,18 +2493,27 @@
           <t xml:space="preserve">https://scholar.google.com/citations?user=d1tT_fEAAAAJ&amp;hl=en </t>
         </is>
       </c>
-      <c r="G36" s="2" t="n">
-        <v>367</v>
-      </c>
-      <c r="H36" s="2" t="n">
+      <c r="G36" t="n">
+        <v>669</v>
+      </c>
+      <c r="H36" t="n">
+        <v>15</v>
+      </c>
+      <c r="I36" t="n">
+        <v>17</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>380</v>
+      </c>
+      <c r="K36" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="I36" s="2" t="n">
+      <c r="L36" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:21:34</t>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:53:19</t>
         </is>
       </c>
     </row>
@@ -2218,18 +2548,27 @@
           <t>https://scholar.google.com/citations?user=N0dZKhYAAAAJ&amp;hl=en&amp;oi=sra</t>
         </is>
       </c>
-      <c r="G37" s="2" t="n">
-        <v>1457</v>
-      </c>
-      <c r="H37" s="2" t="n">
+      <c r="G37" t="n">
+        <v>3742</v>
+      </c>
+      <c r="H37" t="n">
+        <v>32</v>
+      </c>
+      <c r="I37" t="n">
+        <v>78</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>1497</v>
+      </c>
+      <c r="K37" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="I37" s="2" t="n">
+      <c r="L37" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:21:47</t>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:53:30</t>
         </is>
       </c>
     </row>
@@ -2264,18 +2603,27 @@
           <t>https://scholar.google.com/citations?hl=en&amp;user=ypPs4YAAAAAJ</t>
         </is>
       </c>
-      <c r="G38" s="2" t="n">
-        <v>1580</v>
-      </c>
-      <c r="H38" s="2" t="n">
+      <c r="G38" t="n">
+        <v>2579</v>
+      </c>
+      <c r="H38" t="n">
+        <v>26</v>
+      </c>
+      <c r="I38" t="n">
+        <v>42</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>1643</v>
+      </c>
+      <c r="K38" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="I38" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:22:01</t>
+      <c r="L38" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:53:39</t>
         </is>
       </c>
     </row>
@@ -2310,18 +2658,27 @@
           <t>https://scholar.google.com/citations?user=YejKuKIAAAAJ&amp;hl=en&amp;oi=ao</t>
         </is>
       </c>
-      <c r="G39" s="2" t="n">
-        <v>408</v>
-      </c>
-      <c r="H39" s="2" t="n">
+      <c r="G39" t="n">
+        <v>3369</v>
+      </c>
+      <c r="H39" t="n">
+        <v>31</v>
+      </c>
+      <c r="I39" t="n">
+        <v>53</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>419</v>
+      </c>
+      <c r="K39" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="I39" s="2" t="n">
+      <c r="L39" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:22:16</t>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:53:51</t>
         </is>
       </c>
     </row>
@@ -2356,18 +2713,27 @@
           <t>https://scholar.google.com/citations?user=lFeQCOEAAAAJ&amp;hl=en&amp;oi=ao</t>
         </is>
       </c>
-      <c r="G40" s="2" t="n">
-        <v>3758</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>88</v>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:22:25</t>
+      <c r="G40" t="n">
+        <v>7319</v>
+      </c>
+      <c r="H40" t="n">
+        <v>42</v>
+      </c>
+      <c r="I40" t="n">
+        <v>119</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>3856</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:54:02</t>
         </is>
       </c>
     </row>
@@ -2402,18 +2768,27 @@
           <t>https://scholar.google.com/citations?hl=en&amp;user=BHdqafUAAAAJ</t>
         </is>
       </c>
-      <c r="G41" s="2" t="n">
-        <v>3116</v>
-      </c>
-      <c r="H41" s="2" t="n">
+      <c r="G41" t="n">
+        <v>4091</v>
+      </c>
+      <c r="H41" t="n">
+        <v>32</v>
+      </c>
+      <c r="I41" t="n">
+        <v>47</v>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>3280</v>
+      </c>
+      <c r="K41" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="I41" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:22:38</t>
+      <c r="L41" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:54:18</t>
         </is>
       </c>
     </row>
@@ -2448,9 +2823,9 @@
           <t>none</t>
         </is>
       </c>
-      <c r="G42" s="2" t="n"/>
-      <c r="H42" s="2" t="n"/>
-      <c r="I42" s="2" t="n"/>
+      <c r="J42" s="2" t="n"/>
+      <c r="K42" s="2" t="n"/>
+      <c r="L42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2483,18 +2858,27 @@
           <t>https://scholar.google.com/citations?user=1ev4piEAAAAJ&amp;hl=en</t>
         </is>
       </c>
-      <c r="G43" s="2" t="n">
-        <v>693</v>
-      </c>
-      <c r="H43" s="2" t="n">
+      <c r="G43" t="n">
+        <v>853</v>
+      </c>
+      <c r="H43" t="n">
         <v>13</v>
       </c>
-      <c r="I43" s="2" t="n">
+      <c r="I43" t="n">
+        <v>19</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>720</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="L43" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:22:45</t>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:54:32</t>
         </is>
       </c>
     </row>
@@ -2529,18 +2913,27 @@
           <t>https://scholar.google.com/citations?hl=en&amp;user=92XOTJMAAAAJ</t>
         </is>
       </c>
-      <c r="G44" s="2" t="n">
-        <v>272</v>
-      </c>
-      <c r="H44" s="2" t="n">
+      <c r="G44" t="n">
+        <v>383</v>
+      </c>
+      <c r="H44" t="n">
         <v>9</v>
       </c>
-      <c r="I44" s="2" t="n">
+      <c r="I44" t="n">
         <v>8</v>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:22:53</t>
+      <c r="J44" s="2" t="n">
+        <v>283</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:54:46</t>
         </is>
       </c>
     </row>
@@ -2575,18 +2968,27 @@
           <t>https://scholar.google.com/citations?user=XfzPXvkAAAAJ&amp;hl=en&amp;oi=ao</t>
         </is>
       </c>
-      <c r="G45" s="2" t="n">
-        <v>445</v>
-      </c>
-      <c r="H45" s="2" t="n">
+      <c r="G45" t="n">
+        <v>635</v>
+      </c>
+      <c r="H45" t="n">
+        <v>11</v>
+      </c>
+      <c r="I45" t="n">
+        <v>13</v>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>461</v>
+      </c>
+      <c r="K45" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="I45" s="2" t="n">
+      <c r="L45" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:23:07</t>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:54:56</t>
         </is>
       </c>
     </row>
@@ -2621,18 +3023,27 @@
           <t>https://scholar.google.com/citations?hl=en&amp;user=8Xok2tYAAAAJ</t>
         </is>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="G46" t="n">
+        <v>317</v>
+      </c>
+      <c r="H46" t="n">
+        <v>8</v>
+      </c>
+      <c r="I46" t="n">
+        <v>8</v>
+      </c>
+      <c r="J46" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="H46" s="2" t="n">
+      <c r="K46" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I46" s="2" t="n">
+      <c r="L46" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:23:18</t>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:55:03</t>
         </is>
       </c>
     </row>
@@ -2667,18 +3078,27 @@
           <t>https://scholar.google.com/citations?user=1bcYE4EAAAAJ&amp;hl=en&amp;authuser=1</t>
         </is>
       </c>
-      <c r="G47" s="2" t="n">
-        <v>2268</v>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="I47" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:23:25</t>
+      <c r="G47" t="n">
+        <v>2609</v>
+      </c>
+      <c r="H47" t="n">
+        <v>24</v>
+      </c>
+      <c r="I47" t="n">
+        <v>39</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>2356</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:55:18</t>
         </is>
       </c>
     </row>
@@ -2713,18 +3133,27 @@
           <t>https://scholar.google.com/citations?user=QVio4JwAAAAJ&amp;hl=en</t>
         </is>
       </c>
-      <c r="G48" s="2" t="n">
-        <v>2259</v>
-      </c>
-      <c r="H48" s="2" t="n">
+      <c r="G48" t="n">
+        <v>3767</v>
+      </c>
+      <c r="H48" t="n">
+        <v>35</v>
+      </c>
+      <c r="I48" t="n">
+        <v>68</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>2322</v>
+      </c>
+      <c r="K48" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="I48" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:23:38</t>
+      <c r="L48" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:55:32</t>
         </is>
       </c>
     </row>
@@ -2759,18 +3188,27 @@
           <t>https://scholar.google.com/citations?user=F8sD3foAAAAJ&amp;hl=en&amp;oi=ao</t>
         </is>
       </c>
-      <c r="G49" s="2" t="n">
-        <v>1205</v>
-      </c>
-      <c r="H49" s="2" t="n">
+      <c r="G49" t="n">
+        <v>4503</v>
+      </c>
+      <c r="H49" t="n">
+        <v>25</v>
+      </c>
+      <c r="I49" t="n">
+        <v>37</v>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>1254</v>
+      </c>
+      <c r="K49" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="I49" s="2" t="n">
+      <c r="L49" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:23:52</t>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:55:47</t>
         </is>
       </c>
     </row>
@@ -2805,18 +3243,27 @@
           <t>https://scholar.google.com/citations?user=dYc-fCgAAAAJ&amp;hl=en&amp;oi=ao</t>
         </is>
       </c>
-      <c r="G50" s="2" t="n">
-        <v>166</v>
-      </c>
-      <c r="H50" s="2" t="n">
+      <c r="G50" t="n">
+        <v>210</v>
+      </c>
+      <c r="H50" t="n">
+        <v>8</v>
+      </c>
+      <c r="I50" t="n">
+        <v>6</v>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>171</v>
+      </c>
+      <c r="K50" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="I50" s="2" t="n">
+      <c r="L50" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:23:57</t>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:56:01</t>
         </is>
       </c>
     </row>
@@ -2851,18 +3298,27 @@
           <t xml:space="preserve">https://scholar.google.com/citations?hl=en&amp;user=UfWevrkAAAAJ </t>
         </is>
       </c>
-      <c r="G51" s="2" t="n">
-        <v>131</v>
-      </c>
-      <c r="H51" s="2" t="n">
+      <c r="G51" t="n">
+        <v>202</v>
+      </c>
+      <c r="H51" t="n">
+        <v>8</v>
+      </c>
+      <c r="I51" t="n">
         <v>7</v>
       </c>
-      <c r="I51" s="2" t="n">
+      <c r="J51" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L51" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:24:04</t>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:56:15</t>
         </is>
       </c>
     </row>
@@ -2897,18 +3353,27 @@
           <t>https://scholar.google.com/citations?user=MsYzuF8AAAAJ&amp;hl=en&amp;oi=ao</t>
         </is>
       </c>
-      <c r="G52" s="2" t="n">
-        <v>1046</v>
-      </c>
-      <c r="H52" s="2" t="n">
+      <c r="G52" t="n">
+        <v>1191</v>
+      </c>
+      <c r="H52" t="n">
+        <v>16</v>
+      </c>
+      <c r="I52" t="n">
+        <v>21</v>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>1115</v>
+      </c>
+      <c r="K52" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="I52" s="2" t="n">
+      <c r="L52" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:24:17</t>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:56:20</t>
         </is>
       </c>
     </row>
@@ -2943,18 +3408,27 @@
           <t>https://scholar.google.com/citations?user=M6Qms2gAAAAJ&amp;hl=en&amp;oi=sra</t>
         </is>
       </c>
-      <c r="G53" s="2" t="n">
-        <v>2837</v>
-      </c>
-      <c r="H53" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="I53" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:24:26</t>
+      <c r="G53" t="n">
+        <v>7227</v>
+      </c>
+      <c r="H53" t="n">
+        <v>42</v>
+      </c>
+      <c r="I53" t="n">
+        <v>168</v>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>2941</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:56:35</t>
         </is>
       </c>
     </row>
@@ -2989,18 +3463,27 @@
           <t>https://scholar.google.com/citations?user=o2U40BEAAAAJ&amp;hl=en&amp;oi=sra</t>
         </is>
       </c>
-      <c r="G54" s="2" t="n">
-        <v>4394</v>
-      </c>
-      <c r="H54" s="2" t="n">
+      <c r="G54" t="n">
+        <v>7710</v>
+      </c>
+      <c r="H54" t="n">
+        <v>45</v>
+      </c>
+      <c r="I54" t="n">
+        <v>98</v>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>4507</v>
+      </c>
+      <c r="K54" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="I54" s="2" t="n">
+      <c r="L54" s="2" t="n">
         <v>87</v>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:24:33</t>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:56:46</t>
         </is>
       </c>
     </row>
@@ -3035,18 +3518,27 @@
           <t>https://scholar.google.com/citations?hl=en&amp;user=yAQesbwAAAAJ</t>
         </is>
       </c>
-      <c r="G55" s="2" t="n">
-        <v>284</v>
-      </c>
-      <c r="H55" s="2" t="n">
+      <c r="G55" t="n">
+        <v>389</v>
+      </c>
+      <c r="H55" t="n">
+        <v>7</v>
+      </c>
+      <c r="I55" t="n">
         <v>6</v>
       </c>
-      <c r="I55" s="2" t="n">
+      <c r="J55" s="2" t="n">
+        <v>292</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L55" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:24:45</t>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:57:00</t>
         </is>
       </c>
     </row>
@@ -3081,18 +3573,27 @@
           <t>https://scholar.google.com/citations?user=T5WaEcIAAAAJ&amp;hl=en&amp;oi=ao</t>
         </is>
       </c>
-      <c r="G56" s="2" t="n">
-        <v>142</v>
-      </c>
-      <c r="H56" s="2" t="n">
+      <c r="G56" t="n">
+        <v>376</v>
+      </c>
+      <c r="H56" t="n">
+        <v>10</v>
+      </c>
+      <c r="I56" t="n">
+        <v>10</v>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="K56" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="I56" s="2" t="n">
+      <c r="L56" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:24:55</t>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:57:14</t>
         </is>
       </c>
     </row>
@@ -3127,18 +3628,27 @@
           <t xml:space="preserve">https://scholar.google.com/citations?user=XZm1OrkAAAAJ&amp;hl=en </t>
         </is>
       </c>
-      <c r="G57" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="H57" s="2" t="n">
+      <c r="G57" t="n">
+        <v>16</v>
+      </c>
+      <c r="H57" t="n">
         <v>2</v>
       </c>
-      <c r="I57" s="2" t="n">
+      <c r="I57" t="n">
         <v>1</v>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:25:01</t>
+      <c r="J57" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:57:23</t>
         </is>
       </c>
     </row>
@@ -3173,18 +3683,27 @@
           <t>https://scholar.google.com/citations?user=2b0a6D0AAAAJ&amp;hl=en&amp;oi=ao</t>
         </is>
       </c>
-      <c r="G58" s="2" t="n">
-        <v>1933</v>
-      </c>
-      <c r="H58" s="2" t="n">
+      <c r="G58" t="n">
+        <v>4931</v>
+      </c>
+      <c r="H58" t="n">
+        <v>27</v>
+      </c>
+      <c r="I58" t="n">
+        <v>37</v>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>1988</v>
+      </c>
+      <c r="K58" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="I58" s="2" t="n">
+      <c r="L58" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:25:09</t>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:57:38</t>
         </is>
       </c>
     </row>
@@ -3219,18 +3738,27 @@
           <t xml:space="preserve">https://scholar.google.com/citations?user=sfyjBj0AAAAJ&amp;hl=en </t>
         </is>
       </c>
-      <c r="G59" s="2" t="n">
-        <v>509</v>
-      </c>
-      <c r="H59" s="2" t="n">
+      <c r="G59" t="n">
+        <v>988</v>
+      </c>
+      <c r="H59" t="n">
+        <v>15</v>
+      </c>
+      <c r="I59" t="n">
+        <v>17</v>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>525</v>
+      </c>
+      <c r="K59" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="I59" s="2" t="n">
+      <c r="L59" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:25:20</t>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:57:53</t>
         </is>
       </c>
     </row>
@@ -3265,18 +3793,27 @@
           <t xml:space="preserve">https://scholar.google.com/citations?user=e00yPXgAAAAJ&amp;hl=en </t>
         </is>
       </c>
-      <c r="G60" s="2" t="n">
-        <v>1023</v>
-      </c>
-      <c r="H60" s="2" t="n">
+      <c r="G60" t="n">
+        <v>1302</v>
+      </c>
+      <c r="H60" t="n">
+        <v>19</v>
+      </c>
+      <c r="I60" t="n">
+        <v>27</v>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>1079</v>
+      </c>
+      <c r="K60" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="I60" s="2" t="n">
+      <c r="L60" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:25:30</t>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:58:02</t>
         </is>
       </c>
     </row>
@@ -3311,18 +3848,27 @@
           <t>https://scholar.google.com/citations?user=L36KAIMAAAAJ&amp;hl=en</t>
         </is>
       </c>
-      <c r="G61" s="2" t="n">
-        <v>2226</v>
-      </c>
-      <c r="H61" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="I61" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:25:40</t>
+      <c r="G61" t="n">
+        <v>3539</v>
+      </c>
+      <c r="H61" t="n">
+        <v>32</v>
+      </c>
+      <c r="I61" t="n">
+        <v>67</v>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>2302</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:58:15</t>
         </is>
       </c>
     </row>
@@ -3357,18 +3903,27 @@
           <t>https://scholar.google.com/citations?user=nksKEqIAAAAJ&amp;hl=en&amp;oi=ao</t>
         </is>
       </c>
-      <c r="G62" s="2" t="n">
-        <v>1547</v>
-      </c>
-      <c r="H62" s="2" t="n">
+      <c r="G62" t="n">
+        <v>5204</v>
+      </c>
+      <c r="H62" t="n">
+        <v>37</v>
+      </c>
+      <c r="I62" t="n">
+        <v>56</v>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>1584</v>
+      </c>
+      <c r="K62" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="I62" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:25:46</t>
+      <c r="L62" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:58:26</t>
         </is>
       </c>
     </row>
@@ -3403,18 +3958,27 @@
           <t>https://scholar.google.com/citations?user=XTBMj9wAAAAJ</t>
         </is>
       </c>
-      <c r="G63" s="2" t="n">
-        <v>1170</v>
-      </c>
-      <c r="H63" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="I63" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:25:58</t>
+      <c r="G63" t="n">
+        <v>1369</v>
+      </c>
+      <c r="H63" t="n">
+        <v>22</v>
+      </c>
+      <c r="I63" t="n">
+        <v>34</v>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>1215</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:58:37</t>
         </is>
       </c>
     </row>
@@ -3449,18 +4013,27 @@
           <t>https://scholar.google.com/citations?user=1FdmxoYAAAAJ&amp;hl=en&amp;oi=ao</t>
         </is>
       </c>
-      <c r="G64" s="2" t="n">
-        <v>298</v>
-      </c>
-      <c r="H64" s="2" t="n">
+      <c r="G64" t="n">
+        <v>1165</v>
+      </c>
+      <c r="H64" t="n">
+        <v>15</v>
+      </c>
+      <c r="I64" t="n">
+        <v>23</v>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>304</v>
+      </c>
+      <c r="K64" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="I64" s="2" t="n">
+      <c r="L64" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:26:08</t>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:58:46</t>
         </is>
       </c>
     </row>
@@ -3495,18 +4068,27 @@
           <t>https://scholar.google.com/citations?user=h7Mm9WoAAAAJ&amp;hl=en&amp;oi=ao</t>
         </is>
       </c>
-      <c r="G65" s="2" t="n">
-        <v>7256</v>
-      </c>
-      <c r="H65" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="I65" s="2" t="n">
-        <v>161</v>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:26:20</t>
+      <c r="G65" t="n">
+        <v>18645</v>
+      </c>
+      <c r="H65" t="n">
+        <v>69</v>
+      </c>
+      <c r="I65" t="n">
+        <v>218</v>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>7447</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>163</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:58:51</t>
         </is>
       </c>
     </row>
@@ -3541,18 +4123,27 @@
           <t>https://scholar.google.com/citations?user=fOmO29kAAAAJ&amp;hl=en&amp;oi=sra</t>
         </is>
       </c>
-      <c r="G66" s="2" t="n">
-        <v>1262</v>
-      </c>
-      <c r="H66" s="2" t="n">
+      <c r="G66" t="n">
+        <v>3537</v>
+      </c>
+      <c r="H66" t="n">
+        <v>31</v>
+      </c>
+      <c r="I66" t="n">
+        <v>81</v>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>1310</v>
+      </c>
+      <c r="K66" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="I66" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:26:26</t>
+      <c r="L66" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:59:02</t>
         </is>
       </c>
     </row>
@@ -3587,18 +4178,27 @@
           <t>https://scholar.google.com/citations?user=J1my6MsAAAAJ&amp;hl=en&amp;oi=ao</t>
         </is>
       </c>
-      <c r="G67" s="2" t="n">
-        <v>2190</v>
-      </c>
-      <c r="H67" s="2" t="n">
+      <c r="G67" t="n">
+        <v>4463</v>
+      </c>
+      <c r="H67" t="n">
+        <v>38</v>
+      </c>
+      <c r="I67" t="n">
+        <v>82</v>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>2246</v>
+      </c>
+      <c r="K67" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="I67" s="2" t="n">
+      <c r="L67" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:26:41</t>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:59:07</t>
         </is>
       </c>
     </row>
@@ -3633,18 +4233,27 @@
           <t>https://scholar.google.com/citations?hl=en&amp;user=rjShXrsAAAAJ</t>
         </is>
       </c>
-      <c r="G68" s="2" t="n">
-        <v>164</v>
-      </c>
-      <c r="H68" s="2" t="n">
+      <c r="G68" t="n">
+        <v>327</v>
+      </c>
+      <c r="H68" t="n">
+        <v>10</v>
+      </c>
+      <c r="I68" t="n">
+        <v>11</v>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="K68" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="I68" s="2" t="n">
+      <c r="L68" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:26:54</t>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:59:18</t>
         </is>
       </c>
     </row>
@@ -3679,18 +4288,27 @@
           <t>https://scholar.google.com/citations?hl=en&amp;user=A1yD-EkAAAAJ</t>
         </is>
       </c>
-      <c r="G69" s="2" t="n">
-        <v>536</v>
-      </c>
-      <c r="H69" s="2" t="n">
+      <c r="G69" t="n">
+        <v>1698</v>
+      </c>
+      <c r="H69" t="n">
+        <v>13</v>
+      </c>
+      <c r="I69" t="n">
+        <v>14</v>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>555</v>
+      </c>
+      <c r="K69" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="I69" s="2" t="n">
+      <c r="L69" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:27:06</t>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:59:26</t>
         </is>
       </c>
     </row>
@@ -3725,18 +4343,27 @@
           <t>https://scholar.google.com/citations?user=qRQ8LQUAAAAJ&amp;hl=en&amp;oi=ao</t>
         </is>
       </c>
-      <c r="G70" s="2" t="n">
-        <v>502</v>
-      </c>
-      <c r="H70" s="2" t="n">
+      <c r="G70" t="n">
+        <v>792</v>
+      </c>
+      <c r="H70" t="n">
+        <v>13</v>
+      </c>
+      <c r="I70" t="n">
+        <v>15</v>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>519</v>
+      </c>
+      <c r="K70" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="I70" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:27:17</t>
+      <c r="L70" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:59:31</t>
         </is>
       </c>
     </row>
@@ -3771,18 +4398,27 @@
           <t>https://scholar.google.com/citations?user=-2N74-UAAAAJ&amp;hl=en&amp;oi=ao</t>
         </is>
       </c>
-      <c r="G71" s="2" t="n">
-        <v>4058</v>
-      </c>
-      <c r="H71" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="I71" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:27:26</t>
+      <c r="G71" t="n">
+        <v>8575</v>
+      </c>
+      <c r="H71" t="n">
+        <v>44</v>
+      </c>
+      <c r="I71" t="n">
+        <v>81</v>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>4209</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:59:41</t>
         </is>
       </c>
     </row>
@@ -3817,18 +4453,27 @@
           <t>https://scholar.google.com/citations?user=HK7RlcQAAAAJ&amp;hl=en</t>
         </is>
       </c>
-      <c r="G72" s="2" t="n">
-        <v>316</v>
-      </c>
-      <c r="H72" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="I72" s="2" t="n">
+      <c r="G72" t="n">
+        <v>332</v>
+      </c>
+      <c r="H72" t="n">
         <v>8</v>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:27:40</t>
+      <c r="I72" t="n">
+        <v>8</v>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>322</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>2026-09-15 10:59:49</t>
         </is>
       </c>
     </row>
@@ -3863,18 +4508,27 @@
           <t>https://scholar.google.com/citations?hl=en&amp;user=dyfZLOgAAAAJ</t>
         </is>
       </c>
-      <c r="G73" s="2" t="n">
-        <v>1415</v>
-      </c>
-      <c r="H73" s="2" t="n">
+      <c r="G73" t="n">
+        <v>6260</v>
+      </c>
+      <c r="H73" t="n">
+        <v>40</v>
+      </c>
+      <c r="I73" t="n">
+        <v>99</v>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>1441</v>
+      </c>
+      <c r="K73" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="I73" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:27:55</t>
+      <c r="L73" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>2026-09-15 11:00:04</t>
         </is>
       </c>
     </row>
@@ -3909,18 +4563,27 @@
           <t>https://scholar.google.com/citations?user=tWSSx0oAAAAJ&amp;hl=en</t>
         </is>
       </c>
-      <c r="G74" s="2" t="n">
-        <v>345</v>
-      </c>
-      <c r="H74" s="2" t="n">
+      <c r="G74" t="n">
+        <v>1624</v>
+      </c>
+      <c r="H74" t="n">
+        <v>20</v>
+      </c>
+      <c r="I74" t="n">
+        <v>49</v>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>362</v>
+      </c>
+      <c r="K74" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="I74" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:28:05</t>
+      <c r="L74" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>2026-09-15 11:00:17</t>
         </is>
       </c>
     </row>
@@ -3955,18 +4618,27 @@
           <t>https://scholar.google.com/citations?user=Wo4uf8cAAAAJ&amp;hl=en&amp;oi=ao</t>
         </is>
       </c>
-      <c r="G75" s="2" t="n">
-        <v>1320</v>
-      </c>
-      <c r="H75" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="I75" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:28:18</t>
+      <c r="G75" t="n">
+        <v>1728</v>
+      </c>
+      <c r="H75" t="n">
+        <v>17</v>
+      </c>
+      <c r="I75" t="n">
+        <v>24</v>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>1360</v>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>2026-09-15 11:00:26</t>
         </is>
       </c>
     </row>
@@ -4001,18 +4673,27 @@
           <t>https://scholar.google.com/citations?user=ZflPbbQAAAAJ&amp;hl=en&amp;oi=ao</t>
         </is>
       </c>
-      <c r="G76" s="2" t="n">
-        <v>1587</v>
-      </c>
-      <c r="H76" s="2" t="n">
+      <c r="G76" t="n">
+        <v>2747</v>
+      </c>
+      <c r="H76" t="n">
+        <v>19</v>
+      </c>
+      <c r="I76" t="n">
+        <v>33</v>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>1620</v>
+      </c>
+      <c r="K76" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="I76" s="2" t="n">
+      <c r="L76" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:28:24</t>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>2026-09-15 11:00:39</t>
         </is>
       </c>
     </row>
@@ -4047,18 +4728,27 @@
           <t>https://scholar.google.com/citations?user=z6fIJ9kAAAAJ&amp;hl=en&amp;oi=ao</t>
         </is>
       </c>
-      <c r="G77" s="2" t="n">
-        <v>4483</v>
-      </c>
-      <c r="H77" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="I77" s="2" t="n">
+      <c r="G77" t="n">
+        <v>16432</v>
+      </c>
+      <c r="H77" t="n">
+        <v>60</v>
+      </c>
+      <c r="I77" t="n">
+        <v>158</v>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>4561</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="L77" s="2" t="n">
         <v>64</v>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:28:34</t>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>2026-09-15 11:00:48</t>
         </is>
       </c>
     </row>
@@ -4093,18 +4783,27 @@
           <t>https://scholar.google.com/citations?hl=en&amp;user=IF9Yq5YAAAAJ</t>
         </is>
       </c>
-      <c r="G78" s="2" t="n">
-        <v>739</v>
-      </c>
-      <c r="H78" s="2" t="n">
+      <c r="G78" t="n">
+        <v>1212</v>
+      </c>
+      <c r="H78" t="n">
+        <v>17</v>
+      </c>
+      <c r="I78" t="n">
+        <v>20</v>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>754</v>
+      </c>
+      <c r="K78" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="I78" s="2" t="n">
+      <c r="L78" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:28:45</t>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>2026-09-15 11:01:00</t>
         </is>
       </c>
     </row>
@@ -4139,18 +4838,27 @@
           <t>https://scholar.google.com/citations?user=_UOiIFMAAAAJ&amp;hl=en</t>
         </is>
       </c>
-      <c r="G79" s="2" t="n">
+      <c r="G79" t="n">
+        <v>92</v>
+      </c>
+      <c r="H79" t="n">
+        <v>3</v>
+      </c>
+      <c r="I79" t="n">
+        <v>3</v>
+      </c>
+      <c r="J79" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="H79" s="2" t="n">
+      <c r="K79" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="I79" s="2" t="n">
+      <c r="L79" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:29:00</t>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>2026-09-15 11:01:16</t>
         </is>
       </c>
     </row>
@@ -4185,18 +4893,27 @@
           <t xml:space="preserve">https://scholar.google.com/citations?hl=en&amp;user=Px5cT9IAAAAJ&amp;view_op=list_works&amp;sortby=pubdate </t>
         </is>
       </c>
-      <c r="G80" s="2" t="n">
-        <v>637</v>
-      </c>
-      <c r="H80" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="I80" s="2" t="n">
+      <c r="G80" t="n">
+        <v>993</v>
+      </c>
+      <c r="H80" t="n">
+        <v>16</v>
+      </c>
+      <c r="I80" t="n">
+        <v>21</v>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>683</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="L80" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:29:07</t>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>2026-09-15 11:01:25</t>
         </is>
       </c>
     </row>
@@ -4231,18 +4948,27 @@
           <t>https://scholar.google.com/citations?user=9FV1v6gAAAAJ&amp;hl=en&amp;oi=ao</t>
         </is>
       </c>
-      <c r="G81" s="2" t="n">
-        <v>1395</v>
-      </c>
-      <c r="H81" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I81" s="2" t="n">
+      <c r="G81" t="n">
+        <v>4151</v>
+      </c>
+      <c r="H81" t="n">
+        <v>28</v>
+      </c>
+      <c r="I81" t="n">
+        <v>45</v>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>1423</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="L81" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:29:17</t>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>2026-09-15 11:01:38</t>
         </is>
       </c>
     </row>
@@ -4277,18 +5003,27 @@
           <t>https://scholar.google.com/citations?user=ZoZohG4AAAAJ&amp;hl=en&amp;oi=ao</t>
         </is>
       </c>
-      <c r="G82" s="2" t="n">
-        <v>3540</v>
-      </c>
-      <c r="H82" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="I82" s="2" t="n">
+      <c r="G82" t="n">
+        <v>9342</v>
+      </c>
+      <c r="H82" t="n">
+        <v>41</v>
+      </c>
+      <c r="I82" t="n">
+        <v>65</v>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>3652</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="L82" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:29:29</t>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>2026-09-15 11:01:52</t>
         </is>
       </c>
     </row>
@@ -4323,18 +5058,27 @@
           <t>https://scholar.google.com/citations?user=BHKT7cgAAAAJ&amp;hl=en&amp;oi=ao</t>
         </is>
       </c>
-      <c r="G83" s="2" t="n">
-        <v>727</v>
-      </c>
-      <c r="H83" s="2" t="n">
+      <c r="G83" t="n">
+        <v>1104</v>
+      </c>
+      <c r="H83" t="n">
+        <v>19</v>
+      </c>
+      <c r="I83" t="n">
+        <v>31</v>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>762</v>
+      </c>
+      <c r="K83" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="I83" s="2" t="n">
+      <c r="L83" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:29:34</t>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>2026-09-15 11:02:05</t>
         </is>
       </c>
     </row>
@@ -4369,18 +5113,27 @@
           <t>https://scholar.google.com/citations?user=WfJBiOAAAAAJ&amp;hl=en</t>
         </is>
       </c>
-      <c r="G84" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="H84" s="2" t="n">
+      <c r="G84" t="n">
+        <v>64</v>
+      </c>
+      <c r="H84" t="n">
         <v>5</v>
       </c>
-      <c r="I84" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:29:46</t>
+      <c r="I84" t="n">
+        <v>3</v>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>2026-09-15 11:02:11</t>
         </is>
       </c>
     </row>
@@ -4415,18 +5168,27 @@
           <t>https://scholar.google.com/citations?hl=en&amp;user=WzRm0WIAAAAJ</t>
         </is>
       </c>
-      <c r="G85" s="2" t="n">
-        <v>971</v>
-      </c>
-      <c r="H85" s="2" t="n">
+      <c r="G85" t="n">
+        <v>4463</v>
+      </c>
+      <c r="H85" t="n">
+        <v>24</v>
+      </c>
+      <c r="I85" t="n">
+        <v>33</v>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>989</v>
+      </c>
+      <c r="K85" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="I85" s="2" t="n">
+      <c r="L85" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:29:55</t>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>2026-09-15 11:02:22</t>
         </is>
       </c>
     </row>
@@ -4461,18 +5223,27 @@
           <t>https://scholar.google.com/citations?hl=en&amp;user=rxXFB9EAAAAJ&amp;view_op=list_works&amp;sortby=pubdate</t>
         </is>
       </c>
-      <c r="G86" s="2" t="n">
-        <v>781</v>
-      </c>
-      <c r="H86" s="2" t="n">
+      <c r="G86" t="n">
+        <v>1161</v>
+      </c>
+      <c r="H86" t="n">
+        <v>16</v>
+      </c>
+      <c r="I86" t="n">
+        <v>20</v>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>817</v>
+      </c>
+      <c r="K86" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="I86" s="2" t="n">
+      <c r="L86" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:30:07</t>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>2026-09-15 11:02:31</t>
         </is>
       </c>
     </row>
@@ -4507,18 +5278,27 @@
           <t>https://scholar.google.com/citations?user=4dQJ45YAAAAJ&amp;hl=en&amp;oi=ao</t>
         </is>
       </c>
-      <c r="G87" s="2" t="n">
-        <v>712</v>
-      </c>
-      <c r="H87" s="2" t="n">
+      <c r="G87" t="n">
+        <v>1324</v>
+      </c>
+      <c r="H87" t="n">
+        <v>20</v>
+      </c>
+      <c r="I87" t="n">
+        <v>45</v>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>742</v>
+      </c>
+      <c r="K87" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="I87" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:30:21</t>
+      <c r="L87" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>2026-09-15 11:02:40</t>
         </is>
       </c>
     </row>
@@ -4553,18 +5333,27 @@
           <t>https://scholar.google.com/citations?hl=en&amp;user=rbg-HVAAAAAJ</t>
         </is>
       </c>
-      <c r="G88" s="2" t="n">
-        <v>548</v>
-      </c>
-      <c r="H88" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="I88" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:30:31</t>
+      <c r="G88" t="n">
+        <v>605</v>
+      </c>
+      <c r="H88" t="n">
+        <v>15</v>
+      </c>
+      <c r="I88" t="n">
+        <v>19</v>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>577</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>2026-09-15 11:02:50</t>
         </is>
       </c>
     </row>
@@ -4599,13 +5388,13 @@
           <t>https://scholar.google.com/citations?user=ySqciaEAAAAJ&amp;hl=en&amp;oi=ao</t>
         </is>
       </c>
-      <c r="G89" s="2" t="n">
+      <c r="J89" s="2" t="n">
         <v>4201</v>
       </c>
-      <c r="H89" s="2" t="n">
+      <c r="K89" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="I89" s="2" t="n">
+      <c r="L89" s="2" t="n">
         <v>59</v>
       </c>
     </row>
@@ -4640,18 +5429,27 @@
           <t>https://scholar.google.com/citations?user=QzRRcfIAAAAJ&amp;hl=en</t>
         </is>
       </c>
-      <c r="G90" s="2" t="n">
-        <v>3106</v>
-      </c>
-      <c r="H90" s="2" t="n">
+      <c r="G90" t="n">
+        <v>6096</v>
+      </c>
+      <c r="H90" t="n">
+        <v>44</v>
+      </c>
+      <c r="I90" t="n">
+        <v>119</v>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>3215</v>
+      </c>
+      <c r="K90" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="I90" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:31:14</t>
+      <c r="L90" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>2026-09-15 11:03:37</t>
         </is>
       </c>
     </row>
@@ -4686,18 +5484,27 @@
           <t>https://scholar.google.com/citations?hl=en&amp;user=kLOKBgUAAAAJ</t>
         </is>
       </c>
-      <c r="G91" s="2" t="n">
-        <v>498</v>
-      </c>
-      <c r="H91" s="2" t="n">
+      <c r="G91" t="n">
+        <v>1028</v>
+      </c>
+      <c r="H91" t="n">
+        <v>20</v>
+      </c>
+      <c r="I91" t="n">
+        <v>30</v>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>514</v>
+      </c>
+      <c r="K91" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="I91" s="2" t="n">
+      <c r="L91" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:31:29</t>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>2026-09-15 11:03:48</t>
         </is>
       </c>
     </row>
@@ -4732,18 +5539,27 @@
           <t>https://scholar.google.com/citations?user=ZpIaeJgAAAAJ&amp;hl=en</t>
         </is>
       </c>
-      <c r="G92" s="2" t="n">
-        <v>2411</v>
-      </c>
-      <c r="H92" s="2" t="n">
+      <c r="G92" t="n">
+        <v>12776</v>
+      </c>
+      <c r="H92" t="n">
+        <v>55</v>
+      </c>
+      <c r="I92" t="n">
+        <v>119</v>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>2466</v>
+      </c>
+      <c r="K92" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="I92" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:31:42</t>
+      <c r="L92" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>2026-09-15 11:03:55</t>
         </is>
       </c>
     </row>
@@ -4778,18 +5594,27 @@
           <t>https://scholar.google.com/citations?user=0ZZ8xGYAAAAJ&amp;hl=en</t>
         </is>
       </c>
-      <c r="G93" s="2" t="n">
-        <v>1372</v>
-      </c>
-      <c r="H93" s="2" t="n">
+      <c r="G93" t="n">
+        <v>1980</v>
+      </c>
+      <c r="H93" t="n">
         <v>19</v>
       </c>
-      <c r="I93" s="2" t="n">
+      <c r="I93" t="n">
+        <v>24</v>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>1397</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="L93" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>2026-08-04 23:31:54</t>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>2026-09-15 11:04:05</t>
         </is>
       </c>
     </row>
